--- a/user-feedback.xlsx
+++ b/user-feedback.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="151">
   <si>
     <t>Timestamp</t>
   </si>
@@ -22,22 +22,31 @@
     <t>Email Address</t>
   </si>
   <si>
-    <t>Your Stellar Testnet Wallet Address (Starts with G... — find it in your Freighter wallet)</t>
-  </si>
-  <si>
-    <t>Rate TrustChain overall</t>
-  </si>
-  <si>
-    <t>What did you do on TrustChain?</t>
+    <t>Stellar Wallet Address</t>
+  </si>
+  <si>
+    <t>How would you rate TrustChain overall?</t>
   </si>
   <si>
     <t>What did you like most about TrustChain?</t>
   </si>
   <si>
-    <t>What can be improved?</t>
-  </si>
-  <si>
-    <t>Did Freighter wallet connect successfully?</t>
+    <t>What should we improve or add next?</t>
+  </si>
+  <si>
+    <t>Devyani Sanjay Gofan</t>
+  </si>
+  <si>
+    <t>gofandevyani@gmail.com</t>
+  </si>
+  <si>
+    <t>GDJNUWA6GX3XO6MBS2YYX4Y5MRAB2BKW6CDTERSIIITV2N764TFW4CDD</t>
+  </si>
+  <si>
+    <t>The overall experience is excellent and reliable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No improvements are needed, Everything is working great </t>
   </si>
   <si>
     <t>Yash Annadate</t>
@@ -46,37 +55,259 @@
     <t>yashannadate2005@gmail.com</t>
   </si>
   <si>
-    <t>GBWDGDXAN4AW22OBEQADIOSK2GE7EFNDLZDTBJV6AP33SEPTGNNGFDAE</t>
-  </si>
-  <si>
-    <t>Verified a Worker's Profile</t>
-  </si>
-  <si>
-    <t>Overall best</t>
-  </si>
-  <si>
-    <t>Just keep building and improving whole application</t>
-  </si>
-  <si>
-    <t>Yes, worked perfectly</t>
-  </si>
-  <si>
-    <t>Mrunal Ghorpade</t>
-  </si>
-  <si>
-    <t>mrunalghorpade16@gmail.com</t>
-  </si>
-  <si>
-    <t>GAGKWDKAZYZ7GSK2K6YZGGEDEZXL2GEHDU2NMOAU4AVHSFAVZH336FFX</t>
-  </si>
-  <si>
-    <t>Registered as a Worker</t>
-  </si>
-  <si>
-    <t>Excellent ui</t>
-  </si>
-  <si>
-    <t>Nothing , everything is perfect</t>
+    <t>GAYEPC6K7W4HQLFTCKAFCH56G2DY733MYS23M5URO2LG5EAO7VRP6E6N</t>
+  </si>
+  <si>
+    <t>Helpful application can find trustworthy workers</t>
+  </si>
+  <si>
+    <t>Work on more consise ui and easy to understand for a new users</t>
+  </si>
+  <si>
+    <t>Sanjivani Gofan</t>
+  </si>
+  <si>
+    <t>sanjivanigofan@gmail.com</t>
+  </si>
+  <si>
+    <t>GAKXQKOF3IYX2XPWIMU77SPRMQYMGAZ6GL3MCFUIZEH2J27QMPCAIAMJ</t>
+  </si>
+  <si>
+    <t>I like easy to use interference, the system is well organised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform is already very efficient and well designed no improvement needed </t>
+  </si>
+  <si>
+    <t>Aditya Sanjay Gofan</t>
+  </si>
+  <si>
+    <t>gofanaditya15@gmail.com</t>
+  </si>
+  <si>
+    <t>GBS5ST5JNQIEP6K3MVTI5T2IWNMCJVFQJ34GCBABRZZ2P6F6PWAUUKNP</t>
+  </si>
+  <si>
+    <t>The features are easy to understand and everything work smoothly.</t>
+  </si>
+  <si>
+    <t>Everything looks good and works perfectly.</t>
+  </si>
+  <si>
+    <t>Shubham Golekar</t>
+  </si>
+  <si>
+    <t>shubhamgolekar62021@gmail.com</t>
+  </si>
+  <si>
+    <t>GCIES2OT5DYKTIUNGYR5PZZVQPDXPMWX2FRUV67T3ZUWK6TZODN7ESC2</t>
+  </si>
+  <si>
+    <t>Ui is very good</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Lilavati Gofan</t>
+  </si>
+  <si>
+    <t>gofanleela@gmail.com</t>
+  </si>
+  <si>
+    <t>GBTXRHXN2HRZ4VJFFQLH4722AQNQVJ6LSPTANBG5R3EPPLYIXZEIUDOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is easy to understand and helps complete task quickly </t>
+  </si>
+  <si>
+    <t>Iam satisfied with features and performance so no changes needed</t>
+  </si>
+  <si>
+    <t>Prerana Ravindra More</t>
+  </si>
+  <si>
+    <t>Preru2102@gmail.com</t>
+  </si>
+  <si>
+    <t>GDJRCEDILVHKSHGIMAGD6IW5HXFGL4MI552C7S32SOCIJVTZXVO47EMC</t>
+  </si>
+  <si>
+    <t>I liked the clean design and how easy it is to navigate.</t>
+  </si>
+  <si>
+    <t>Everything is working perfectly no changes needed</t>
+  </si>
+  <si>
+    <t>Priyanka Nanavare</t>
+  </si>
+  <si>
+    <t>nanavarepriyanka0@gmail.com</t>
+  </si>
+  <si>
+    <t>GANI6VCRTRDTBVYPYPZ6C4DXS7ZF3J46ISJPN5WG4Z5MIGUHWG223RQC</t>
+  </si>
+  <si>
+    <t>It's UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add multiple languages </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anuj Patil </t>
+  </si>
+  <si>
+    <t>anuj24darkside@gmail.com</t>
+  </si>
+  <si>
+    <t>GCM5HJ6PGNITCR26FIWDQ62OQ4LTF7HDSMQTXH5GIVOFY7RKM5WR4PC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything is amazing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good </t>
+  </si>
+  <si>
+    <t>Meghiya Tulse</t>
+  </si>
+  <si>
+    <t>meghiyatulse24@gmail.com</t>
+  </si>
+  <si>
+    <t>GAHZT5YQ7TDVHDYOR7LXEMN7BH343KTYGNC2NBY4HXLHRDPR4GVHNRJ2</t>
+  </si>
+  <si>
+    <t>Kartik Botre</t>
+  </si>
+  <si>
+    <t>kartikbotre2410@gmail.com</t>
+  </si>
+  <si>
+    <t>GDCYI5FYG5LUC4TLNPCBAFBTH3ITYTTPZ5M5Z2RC34DIFSUFBORBWJUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flow </t>
+  </si>
+  <si>
+    <t>Nothing right now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stallon Joseph </t>
+  </si>
+  <si>
+    <t>stallonjoseph10@gmail.com</t>
+  </si>
+  <si>
+    <t>GCWD2XRCJFP5AMT57MRYIVEK2QRWZUNUVROGYYRK2XGCZFOORXCXTRW3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I like the UI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add multiple languages options </t>
+  </si>
+  <si>
+    <t>Sanjay Gofan</t>
+  </si>
+  <si>
+    <t>sanjaygofan892@gmail.com</t>
+  </si>
+  <si>
+    <t>GDNMERBNRBKLWKRN475MBFYV6QRSHINSF33O7NXMA2PXVP4LHGU7XUMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well designed the platform and it's easy to understand even for new user </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything is good no additional improvements are required </t>
+  </si>
+  <si>
+    <t>Kajal Mahajan</t>
+  </si>
+  <si>
+    <t>mahajankajal902@gmail.com</t>
+  </si>
+  <si>
+    <t>GDM4C3U5L4JQIXVU76W6PYEBDYB6R23BLS56TIHHVOAYS66DBQJ3T6WC</t>
+  </si>
+  <si>
+    <t>The platform is very simple to use and saves a lot of time.</t>
+  </si>
+  <si>
+    <t>No improvements needed at the moment. The system is already efficient and user-friendly.</t>
+  </si>
+  <si>
+    <t>Manisha khatpe</t>
+  </si>
+  <si>
+    <t>manishakhatpe03@gmail.com</t>
+  </si>
+  <si>
+    <t>GBZVSOQ3M4VFC46JFB6I7IHSSU76MNUDLI62S7KWLTGFGPHHIEVBQEOU</t>
+  </si>
+  <si>
+    <t>I like the idea most</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add QR code option for employees </t>
+  </si>
+  <si>
+    <t>Piyush bawalekar</t>
+  </si>
+  <si>
+    <t>bawlekarpiyush075@gmail.com</t>
+  </si>
+  <si>
+    <t>GB7MWYYW2X7VMKFISLOJQ3CJTSAOFKB3DPLIOIARL4YHKT2AHJ2JJT7A</t>
+  </si>
+  <si>
+    <t>I like the ui and idea</t>
+  </si>
+  <si>
+    <t>Work on adding more options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayush gaikwad </t>
+  </si>
+  <si>
+    <t>ayyush1326@gmail.com</t>
+  </si>
+  <si>
+    <t>GBUDUGMHCM7B54DIB5P5LP4PP6MG7MJ6VUBBYDB53BZNZCTH36LLG5MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique application </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything is great </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Govind mote </t>
+  </si>
+  <si>
+    <t>motegovind75@gmail.com</t>
+  </si>
+  <si>
+    <t>GBNJOKPTB5AUI4RIEGI6KBOEF5O5LDUEKZGFDCFR5QZFCYCG54WT7NEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App ui-ux design is very Nice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khushi Nagare </t>
+  </si>
+  <si>
+    <t>khushinagare8@gmail.com</t>
+  </si>
+  <si>
+    <t>GAYUBQQSVMCPC6UE6YNDAUTBMA7A5Q5EZBZWDHYRYXOPBMV57SQGZU63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything is nice and working properly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ui should be more better but overall everything is good </t>
   </si>
   <si>
     <t>Thanchan Bhumij</t>
@@ -88,58 +319,151 @@
     <t>GDHPNSQINMCUNO6DOWO7HSAW5NTNO2MDY6LDHGKPJMGLUSUMLVWBJKJ6</t>
   </si>
   <si>
-    <t>All of the above</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is secure and provides a clear transparency </t>
-  </si>
-  <si>
-    <t>UI can be improved</t>
-  </si>
-  <si>
-    <t>Priyanka Nanavare</t>
-  </si>
-  <si>
-    <t>nanavarepriyanka0@gmail.com</t>
-  </si>
-  <si>
-    <t>GCM5HJ6PGNITCR26FIWDQ62OQ4LTF7HDSMQTXH5GIVOFY7RKM5WR4PC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The idea of solving real world problems </t>
-  </si>
-  <si>
-    <t xml:space="preserve">I think nothing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anuj Patil </t>
-  </si>
-  <si>
-    <t>anuj24darkside@gmail.com</t>
-  </si>
-  <si>
-    <t>GCFMMVOUOIAMWPOSA4354VADBAW3JFVMGOCJDZWSRDNVR5T6NXY3YAMN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every is good </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some minor changes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sarthak Kharat </t>
-  </si>
-  <si>
-    <t>sarthak01230@gmail.com</t>
-  </si>
-  <si>
-    <t>GBZVSOQ3M4VFC46JFB6I7IHSSU76MNUDLI62S7KWLTGFGPHHIEVBQEOU</t>
-  </si>
-  <si>
-    <t>What I liked most about TrustChain was its intuitive interface and the robust verification system that builds trust among users. The experience felt secure and user‑friendly, encouraging active participation in the worker community.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What can be improved is adding more detailed analytics or insights for workers about their endorsement history, and enhancing notification features for profile verification updates. These tweaks would make the platform even more efficient and informative. </t>
+    <t xml:space="preserve">Transparency </t>
+  </si>
+  <si>
+    <t>Add some attractive things in the homepage interpage</t>
+  </si>
+  <si>
+    <t>Sudam nanavare</t>
+  </si>
+  <si>
+    <t>sudamnanavare007@gmail.com</t>
+  </si>
+  <si>
+    <t>GCSVB74U65GXPWSOXSIOG3AHJQQLARC3UUV4TYOXQ45I6QLOBE56IY2R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplicity </t>
+  </si>
+  <si>
+    <t>Add multiple language support and contact details of worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooja Nanavare </t>
+  </si>
+  <si>
+    <t>poojananavare379@gmail.com</t>
+  </si>
+  <si>
+    <t>GCBQ4RZFJRFPF4SNQBNRMOLMEOOMZDFFRZKPOK752TNQYNFCOUMQFACX</t>
+  </si>
+  <si>
+    <t>Idea of the trust chain and the logic behind it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No need to improvement everything works perfectly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pranali Ganesh Taware </t>
+  </si>
+  <si>
+    <t>tawarepranali33@gmail.com</t>
+  </si>
+  <si>
+    <t>GCWT5GIBSGNAEDVVTDQFVOV6PZ55A2EK4RWTEURLXTI4CE3G4CB2C5QV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything </t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pallavi Patil </t>
+  </si>
+  <si>
+    <t>pallaviii1809@gmail.com</t>
+  </si>
+  <si>
+    <t>GCSXAQUFSIRE2PFXYS27MFRMWAXUVOLCFA6FH6WFKGB57ZLGCRPLFHOJ</t>
+  </si>
+  <si>
+    <t>user-friendly, fast-loading, and mobile-responsive</t>
+  </si>
+  <si>
+    <t>Nothing for now</t>
+  </si>
+  <si>
+    <t>Mayuresh taware</t>
+  </si>
+  <si>
+    <t>freason266@gmail.com</t>
+  </si>
+  <si>
+    <t>GBZGYIQSNMWICQ5RBMAUUKJ4ZJEV7GMNJ2MA4DM3SGGUIBPOJWY364PH</t>
+  </si>
+  <si>
+    <t>Sakshi dhanna</t>
+  </si>
+  <si>
+    <t>sakshidhanna@gmail.com</t>
+  </si>
+  <si>
+    <t>GCQTHX3P3YCIPV7VSDMPK5EHEBOKPZKQXXRERT3PLLIQARQXG7Z2FMII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User friendly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">High speed performance </t>
+  </si>
+  <si>
+    <t>Sagar Khilare</t>
+  </si>
+  <si>
+    <t>skhilare28@gmail.com</t>
+  </si>
+  <si>
+    <t>The certificate is trusted, enabling a secure connection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing </t>
+  </si>
+  <si>
+    <t>Narayan mote</t>
+  </si>
+  <si>
+    <t>totomoto5152@gmail.com</t>
+  </si>
+  <si>
+    <t>GD7KALJCSWSZD4BHZJB5UAI7D5TLK26HAQUGCZEUQCUNUW5IKJGSYDLG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy to use navigation </t>
+  </si>
+  <si>
+    <t>You should update UI</t>
+  </si>
+  <si>
+    <t>Raghav shastri</t>
+  </si>
+  <si>
+    <t>shriraghavshastri@gmail.com</t>
+  </si>
+  <si>
+    <t>GACDEETPASDGWRYNMATJJOEAR54TRBU3HJXXC4GHUSY25ZIGOTHUXVZ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good idea </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You should more work on a logic </t>
+  </si>
+  <si>
+    <t>gauri shinde</t>
+  </si>
+  <si>
+    <t>gaurishinde@gmail.com</t>
+  </si>
+  <si>
+    <t>GBPZYMJNCTRQCVMFVAQSG6Q6PJDORWB2QU2JKGOXRS64NLKHBR7TNACW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simplicity </t>
+  </si>
+  <si>
+    <t>multiple things like Qr code , languages , contact numbers</t>
   </si>
 </sst>
 </file>
@@ -271,17 +595,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I7" displayName="Form_Responses" name="Form_Responses" id="1">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G31" displayName="Form_Responses" name="Form_Responses" id="1">
+  <tableColumns count="7">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Full Name" id="2"/>
     <tableColumn name="Email Address" id="3"/>
-    <tableColumn name="Your Stellar Testnet Wallet Address (Starts with G... — find it in your Freighter wallet)" id="4"/>
-    <tableColumn name="Rate TrustChain overall" id="5"/>
-    <tableColumn name="What did you do on TrustChain?" id="6"/>
-    <tableColumn name="What did you like most about TrustChain?" id="7"/>
-    <tableColumn name="What can be improved?" id="8"/>
-    <tableColumn name="Did Freighter wallet connect successfully?" id="9"/>
+    <tableColumn name="Stellar Wallet Address" id="4"/>
+    <tableColumn name="How would you rate TrustChain overall?" id="5"/>
+    <tableColumn name="What did you like most about TrustChain?" id="6"/>
+    <tableColumn name="What should we improve or add next?" id="7"/>
   </tableColumns>
   <tableStyleInfo name="Form responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -489,13 +811,11 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="3" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="37.63"/>
-    <col customWidth="1" min="5" max="5" width="22.13"/>
-    <col customWidth="1" min="6" max="6" width="28.25"/>
-    <col customWidth="1" min="7" max="7" width="35.38"/>
-    <col customWidth="1" min="8" max="8" width="22.25"/>
-    <col customWidth="1" min="9" max="9" width="35.75"/>
-    <col customWidth="1" min="10" max="15" width="18.88"/>
+    <col customWidth="1" min="4" max="4" width="21.25"/>
+    <col customWidth="1" min="5" max="5" width="33.88"/>
+    <col customWidth="1" min="6" max="6" width="35.38"/>
+    <col customWidth="1" min="7" max="7" width="32.38"/>
+    <col customWidth="1" min="8" max="13" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -520,183 +840,685 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="2">
-        <v>46115.41029425926</v>
+        <v>46122.80480835648</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="2">
-        <v>46115.43134318287</v>
+        <v>46122.809131064816</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="2">
-        <v>46115.455968634255</v>
+        <v>46122.81037983796</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3">
         <v>5.0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="2">
-        <v>46115.625788668985</v>
+        <v>46122.81271650463</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5.0</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="2">
-        <v>46115.63354273148</v>
+        <v>46122.81615680555</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3">
         <v>5.0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2">
-        <v>46115.63777398148</v>
+        <v>46122.816278425926</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="2">
+        <v>46122.820893703705</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E8" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="3" t="s">
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="2">
+        <v>46122.82445354167</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>15</v>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="2">
+        <v>46122.8341987037</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="2">
+        <v>46122.84048491898</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="2">
+        <v>46122.84405561343</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="2">
+        <v>46122.846480671295</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="2">
+        <v>46122.90983091435</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="2">
+        <v>46122.91353950232</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="2">
+        <v>46122.91971408565</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="2">
+        <v>46122.935039965276</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="2">
+        <v>46122.95535427083</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="2">
+        <v>46122.960795439816</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="2">
+        <v>46123.064308472225</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="2">
+        <v>46123.26548263889</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="2">
+        <v>46123.311362650464</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="2">
+        <v>46123.31413943287</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="2">
+        <v>46123.35640722222</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="2">
+        <v>46123.391729525465</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="2">
+        <v>46123.46580503472</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="2">
+        <v>46123.499562627316</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="2">
+        <v>46123.5875393287</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="2">
+        <v>46123.660562881945</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="2">
+        <v>46123.667835995366</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="2">
+        <v>46123.67444263889</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
